--- a/outputs/01.2026/1.2026_final.xlsx
+++ b/outputs/01.2026/1.2026_final.xlsx
@@ -62431,4 +62431,10 @@
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{31b54463-0dc6-4729-9f0b-886b1c3961cf}" enabled="1" method="Standard" siteId="{3dd59dce-9563-4ed5-b9aa-d0320fb1b440}" removed="0"/>
+</clbl:labelList>
 </file>